--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
+        <v>98197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>639119.8173727706</v>
+        <v>639120</v>
       </c>
       <c r="R2" t="n">
-        <v>6925688.572763814</v>
+        <v>6925689</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -762,19 +762,9 @@
           <t>2011-07-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -818,11 +808,11 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
+        <v>98197</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -864,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>638896.8744903825</v>
+        <v>638897</v>
       </c>
       <c r="R3" t="n">
-        <v>6925835.510364137</v>
+        <v>6925836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,19 +892,9 @@
           <t>2011-07-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2011-07-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Y-län Floraväktarna, Olof Svensson, Gudrun Fredén</t>
+          <t>Gudrun Fredén, Y-län Floraväktarna, Olof Svensson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Y-län Floraväktarna, Olof Svensson, Gudrun Fredén</t>
+          <t>Olof Svensson, Y-län Floraväktarna, Gudrun Fredén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gudrun Fredén, Y-län Floraväktarna, Olof Svensson</t>
+          <t>Y-län Floraväktarna, Olof Svensson, Gudrun Fredén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -808,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98197</v>
+        <v>98202</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Olof Svensson, Y-län Floraväktarna, Gudrun Fredén</t>
+          <t>Y-län Floraväktarna, Olof Svensson, Gudrun Fredén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -808,7 +803,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98202</v>
+        <v>98211</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,11 +817,6 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>220787</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -803,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98211</v>
+        <v>98224</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,6 +822,11 @@
       </c>
       <c r="E3" t="n">
         <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98224</v>
+        <v>98237</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98237</v>
+        <v>98240</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98240</v>
+        <v>98241</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98241</v>
+        <v>98244</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 56372-2023 artfynd.xlsx
+++ b/artfynd/A 56372-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3045294</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>3045295</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
